--- a/basedatos_partidas/salida/descompuestos/09.14.01.190.xlsx
+++ b/basedatos_partidas/salida/descompuestos/09.14.01.190.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MT-BOMBA-AGUA</t>
+          <t>MT-FLOTANTE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -551,23 +551,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Bomba centrífuga de agua para suministro doméstico, con su control y accesorios de conexión.</t>
+          <t>Válvula de flotante y accesorios de control de nivel para tanque de agua.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>160</v>
+        <v>9.5</v>
       </c>
       <c r="H10" t="n">
-        <v>80</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT-FLOTANTE</t>
+          <t>MT-VALV-CHECK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -577,23 +577,23 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Válvula de flotante y accesorios de control de nivel para tanque de agua.</t>
+          <t>Válvula de retención y válvula de compuerta para instalación de bombeo.</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>9.5</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>9.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MT-VALV-CHECK</t>
+          <t>MT-PLO-SOP</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -603,115 +603,115 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Válvula de retención y válvula de compuerta para instalación de bombeo.</t>
+          <t>Abrazaderas, soportes y tacos de fijación para tubería.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>0.45</v>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MT-PLO-SOP</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Abrazaderas, soportes y tacos de fijación para tubería.</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal materiales:</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Equipo y maquinaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MQ-TALADRO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Taladro percutor con brocas, incluida amortización y consumo.</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.45</v>
       </c>
-      <c r="H13" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal materiales:</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>105.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>Equipo y maquinaria</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MQ-TALADRO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Taladro percutor con brocas, incluida amortización y consumo.</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.5</v>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal equipo y maquinaria:</t>
+        </is>
       </c>
       <c r="H16" t="n">
         <v>0.45</v>
       </c>
     </row>
     <row r="17">
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal equipo y maquinaria:</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0.45</v>
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Mano de obra</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>Mano de obra</t>
-        </is>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MO-OF1-PLO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Oficial de 1ª plomero.</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MO-OF1-PLO</t>
+          <t>MO-AYU</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -721,100 +721,74 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª plomero.</t>
+          <t>Ayudante.</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MO-AYU</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Ayudante.</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal mano de obra:</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Costes directos complementarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Costes directos complementarios</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal mano de obra:</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>Costes directos complementarios</t>
-        </is>
+      <c r="G22" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="23">
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Costes directos complementarios</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>120.25</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Costes directos (1+2+3+4):</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="5" t="n">
-        <v>121.45</v>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="5" t="n">
+        <v>40.65</v>
       </c>
     </row>
   </sheetData>
